--- a/data/trans_orig/IP31KM04_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM04_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21422</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17267</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25143</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>57,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>46,13%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>67,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>21476</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16503</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26539</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>46,19%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,49%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25451</t>
+          <t>20469</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>25177</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>46927</t>
+          <t>41891</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39388</t>
+          <t>35502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54482</t>
+          <t>48261</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>60,24%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16013</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12292</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20168</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>42,77%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>32,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>53,87%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>25019</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19956</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29992</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>53,81%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>42,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>64,51%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19834</t>
+          <t>22212</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14655</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24932</t>
+          <t>26700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>44852</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37297</t>
+          <t>31855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52391</t>
+          <t>44614</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>55,69%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>84329</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>73723</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>93717</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>53,7%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>46,95%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>59,68%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>73863</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>64155</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>84480</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>46,37%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>40,27%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>53,03%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>96228</t>
+          <t>69347</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85095</t>
+          <t>59506</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107289</t>
+          <t>78780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>170092</t>
+          <t>153676</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155185</t>
+          <t>139991</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>187558</t>
+          <t>167922</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,5%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72713</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>63325</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>83319</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>46,3%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>40,32%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>53,05%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>85436</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>74819</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>95144</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>53,63%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>46,97%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>59,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>85731</t>
+          <t>76171</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74670</t>
+          <t>66738</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>96864</t>
+          <t>86012</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>171167</t>
+          <t>148884</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>153701</t>
+          <t>134638</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>186074</t>
+          <t>162569</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>53,73%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>93033</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>80518</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>106238</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>46,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>40,23%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>53,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>86335</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>76180</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>99606</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>49,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>44,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>97769</t>
+          <t>85275</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84023</t>
+          <t>74164</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112146</t>
+          <t>96646</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>184105</t>
+          <t>178308</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164602</t>
+          <t>161839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199879</t>
+          <t>196366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>52,39%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>107093</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>93888</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>119608</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>53,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>46,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>59,77%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>86737</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>73466</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>96892</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>50,12%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>55,98%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>114721</t>
+          <t>89397</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100344</t>
+          <t>78026</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128467</t>
+          <t>100508</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>201458</t>
+          <t>196490</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>185684</t>
+          <t>178432</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>220961</t>
+          <t>212959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>121514</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>105256</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>143189</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>36,02%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>49,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>96389</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>67095</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>114638</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>127066</t>
+          <t>101499</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107965</t>
+          <t>88574</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>153502</t>
+          <t>116434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>223455</t>
+          <t>223013</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>189515</t>
+          <t>199903</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>254655</t>
+          <t>250171</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>45,69%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>170707</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>149032</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>186965</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>58,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>51,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>63,98%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>177878</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>159629</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>207172</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>64,86%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>58,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>75,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>177933</t>
+          <t>153838</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151497</t>
+          <t>138903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>197034</t>
+          <t>166763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>355811</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>324611</t>
+          <t>297387</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>389751</t>
+          <t>347655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>63,49%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>320299</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>298651</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>346673</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>46,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>43,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>50,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>408</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>278064</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>241923</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>304384</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>42,57%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>37,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>346514</t>
+          <t>276591</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>316080</t>
+          <t>254684</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>374094</t>
+          <t>298384</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>624578</t>
+          <t>596889</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>579463</t>
+          <t>564640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>663286</t>
+          <t>630113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>366525</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>340151</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>388173</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>53,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>49,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>56,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>507</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>375070</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>348750</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>411211</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>57,43%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>53,4%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>62,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>398219</t>
+          <t>341617</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>370639</t>
+          <t>319824</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>428653</t>
+          <t>363524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>773289</t>
+          <t>708142</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>734581</t>
+          <t>674918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>818404</t>
+          <t>740391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>56,73%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
